--- a/learn-java-basic/src/main/resources/最终预期模版样式.xlsx
+++ b/learn-java-basic/src/main/resources/最终预期模版样式.xlsx
@@ -1178,7 +1178,7 @@
         <v>6</v>
       </c>
       <c r="E2" s="5">
-        <v>890</v>
+        <v>1329</v>
       </c>
     </row>
     <row r="3" spans="1:5">

--- a/learn-java-basic/src/main/resources/最终预期模版样式.xlsx
+++ b/learn-java-basic/src/main/resources/最终预期模版样式.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27660" windowHeight="11520"/>
+    <workbookView windowWidth="27360" windowHeight="11520"/>
   </bookViews>
   <sheets>
     <sheet name="大车" sheetId="2" r:id="rId1"/>
@@ -1178,7 +1178,7 @@
         <v>6</v>
       </c>
       <c r="E2" s="5">
-        <v>890</v>
+        <v>1329</v>
       </c>
     </row>
     <row r="3" spans="1:5">
@@ -1476,14 +1476,14 @@
       <c r="B23" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="C23" s="6">
-        <v>-0.063</v>
+      <c r="C23" s="10">
+        <v>-0.05</v>
       </c>
       <c r="D23" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="E23" s="6">
-        <v>-0.063</v>
+      <c r="E23" s="10">
+        <v>-0.05</v>
       </c>
     </row>
     <row r="24" spans="1:5">
